--- a/countries/se-o/2026-2029.xlsx
+++ b/countries/se-o/2026-2029.xlsx
@@ -59980,10 +59980,10 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O422" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U422" t="inlineStr">
         <is>
@@ -60544,10 +60544,10 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U426" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8162</v>
+        <v>8160</v>
       </c>
     </row>
     <row r="16">
